--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AWS Cloud Data Architect</t>
+          <t>Senior Software Engineer (API Integrations)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Davie, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e787928433fb38f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ee6066bc70296362</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Quality</t>
+          <t>AWS Cloud Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Torrance, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=e787928433fb38f9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Senior Data Engineer - Quality</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c02ad439b17c3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, EMR, S3, SQS, SNS, RDS, Databricks, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e02ba02243648f0</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Blockchain Java Backend Developer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=6c02ad439b17c3a6</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
+          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer &amp; Architect</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
+          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Full Stack Developer &amp; Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Linstarsolution corporation</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
         </is>
       </c>
     </row>
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -946,29 +946,29 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
         </is>
       </c>
     </row>
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI - Native Builder</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer (W2 only)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Highbrow Technology Inc</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer I</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, SNS, RDS, Azure, SQL Server, DynamoDB, Splunk</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1eaa43d2708b0fa5</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
+          <t>Senior Azure Data Engineer (W2 only)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Highbrow Technology Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
+          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
+          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0504cd8c91e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c53274a80c0bed</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Database Engineer / Database Administrator</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Forward Deployed Engineer, Energy</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ff0504cd8c91e07a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>MLOps Engineer II</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>ICW Group</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=04c53274a80c0bed</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,67 +2211,67 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Junior Software Developer, Applications</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>O'Fallon, IL, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230c6608eadb69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Snowflake, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc844d637a4a899</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Kafka, NoSQL, Terraform, AWS CloudFormation</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ff4d06117e88a9</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Software Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Junior Software Developer, Applications</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Everforth ECS</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>O'Fallon, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=230c6608eadb69fd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Technical Architect (BIBA)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Hexaware Technologies</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Snowflake, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=ffc844d637a4a899</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Platform Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Kafka, NoSQL, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=78ff4d06117e88a9</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Platform Architect, AI Adoption</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, Scala, Kafka, Snowflake, CI/CD, Docker, Kubernetes</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abf4cabe83b9851e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Epic Clinical Business Intelligence Analyst - Intermediate (On-Site)</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UT Health Science Center at San Antonio</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,29 +2831,29 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, Tableau, Git, Python</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be9f49babb6ca927</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer Remote - US • Remote</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612993f0cf902297</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Senior .net Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>RA Capital Management</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,180 +2946,600 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
+          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Aerospace Software DevOps Engineer II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>Senior Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Bain &amp; Company</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-13</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer Remote - US • Remote</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Daxko</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=612993f0cf902297</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Data Engineer - Consultant</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Releady</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Sr. Associate, Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Community Federal Savings Bank</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Data Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>RA Capital Management</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior AI &amp; Data Engineer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Alamar Biosciences</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fremont, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Senior Data Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Core BTS</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Advanced AI Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>SRE / DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Full-Stack Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Social Impact</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Aerospace Software DevOps Engineer II</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Blue Origin</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
           <t>AI/ML Engineer</t>
         </is>
       </c>
-      <c r="B77" t="inlineStr">
+      <c r="B88" t="inlineStr">
         <is>
           <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
-      <c r="C77" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D77" t="n">
+      <c r="D88" t="n">
         <v>10.4</v>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>

--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer- Local</t>
+          <t>Senior Data Engineer - Quality</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Ai Vantage</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Vienna, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,77 +626,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, RDS, Hadoop</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9f567112b742a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (API Integrations)</t>
+          <t>Senior AWS Cloud Data Engineer I</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Davie, FL, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, SNS, API Gateway, ECS, RDS, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee6066bc70296362</t>
+          <t>https://www.indeed.com/viewjob?jk=d17713297f88b607</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AWS Cloud Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Torrance, CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS, Spark</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e787928433fb38f9</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Quality</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
+          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Blockchain Java Backend Developer</t>
+          <t>Sr Forward Deployed Engineer (Foundry)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, MongoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c02ad439b17c3a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7e98784d3b069887</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AI Full Stack Developer &amp; Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Linstarsolution corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1245fb4aa0b33840</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI Engineer III HYBRID</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RealPage Inc</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,112 +941,112 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Data Modeling, ELT, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=03b9bfbeef45e637</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>System Engineer- Platform/API Gateway</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f3215e173a2f079</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35019214a98b077</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9516aa524f738d9</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI - Native Builder</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d5239019737c1e6</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Marketing Data Operations</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,42 +1196,42 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
@@ -1248,15 +1248,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Azure Data Engineer (W2 only)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Highbrow Technology Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
         </is>
       </c>
     </row>
@@ -1383,12 +1383,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer (W2 only)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Highbrow Technology Inc</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer-Platform/Kafka/Messaging</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>IAM, RDS, GCP, Dataflow, Spark, Scala, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
+          <t>https://www.indeed.com/viewjob?jk=7af3032d6f77f72a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Forward Deployed Engineer, Energy</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
+          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Energy</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,42 +1816,42 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
+          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Analyst - Data Engineering 5A</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Genpact</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, SQS, IAM, RDS, Oracle, MySQL, NoSQL, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ff0504cd8c91e07a</t>
+          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Database Engineer / Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>MLOps Engineer II</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>ICW Group</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Scala, MLOps, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c53274a80c0bed</t>
+          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
+          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Santa Monica, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,14 +2351,14 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
+          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,14 +2386,14 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,17 +2481,17 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Junior Software Developer, Applications</t>
+          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Everforth ECS</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>O'Fallon, IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>ECS, RDS, Scala, Jenkins, Maven, Terraform, Docker, Kubernetes, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=230c6608eadb69fd</t>
+          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Technical Architect (BIBA)</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Hexaware Technologies</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Hadoop, Snowflake, SQL Server, ETL, Talend</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ffc844d637a4a899</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Platform Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, Kafka, NoSQL, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=78ff4d06117e88a9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior .net Software Engineer</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, SQL Server, ETL, ELT, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,234 +2946,234 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f633477012d7720</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Associate, Cloud Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Community Federal Savings Bank</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>RA Capital Management</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior AI &amp; Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Alamar Biosciences</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Fremont, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer Remote - US • Remote</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Daxko</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Scala, SQL Server, MySQL, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=612993f0cf902297</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>SRE / DevOps Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>Full-Stack Platform Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Social Impact</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Aerospace Software DevOps Engineer II</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RA Capital Management</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3330,216 +3330,6 @@
         </is>
       </c>
       <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Advanced AI Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>SRE / DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Full-Stack Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Social Impact</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Aerospace Software DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>

--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,200 +503,200 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GCP Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Google Cloud Platform, GCP, BigQuery, Dataflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-15</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88dfefca6da19496</t>
+          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Quality</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SharkNinja</t>
+          <t>Sidley Austin</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Athena, Step Functions, S3, RDS, Scala, Data Modeling</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4eb47d9c8a787444</t>
+          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AWS Cloud Data Engineer I</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>American Honda Motor</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Marysville, OH, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
+          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
+          <t>https://www.indeed.com/viewjob?jk=d17713297f88b607</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Quality</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AWS Cloud Data Engineer I</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>American Honda Motor</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Marysville, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, Step Functions, S3, IAM, RDS</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17713297f88b607</t>
+          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,94 +706,94 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
+          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Sr Forward Deployed Engineer (Foundry)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Trinity Industries</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=7e98784d3b069887</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
+          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer (Foundry)</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,17 +801,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e98784d3b069887</t>
+          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -841,107 +841,107 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>System Engineer- Platform/API Gateway</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Engineer III HYBRID</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RealPage Inc</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Vertex AI, Scala, Data Modeling, ELT, MLOps, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=03b9bfbeef45e637</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System Engineer- Platform/API Gateway</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, Marketing Data Operations</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Centric Consulting</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
+          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,102 +1091,102 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Azure Data Engineer (W2 only)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Highbrow Technology Inc</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer (W2 only)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Highbrow Technology Inc</t>
+          <t>Freddie Mac</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
+          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Intregration Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>IntegraTouch</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>System Engineer-Platform/Kafka/Messaging</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>IAM, RDS, GCP, Dataflow, Spark, Scala, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=7af3032d6f77f72a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>System Engineer-Platform/Kafka/Messaging</t>
+          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Spark, Scala, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af3032d6f77f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,34 +1641,34 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Forward Deployed Engineer, Energy</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
+          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Energy</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Dearborn, MI, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,42 +1781,42 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
+          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analyst - Data Engineering 5A</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Genpact</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Oracle, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b591868fadbb51ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
+          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Hashout Technologies, Inc.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
+          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Engineer / Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>Goodwill Industries of Ky., Inc.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
+          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Santa Monica, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a89ce09999706a8d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46f97f725c092d19</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Spark, Scala, Snowflake, Data Modeling, ELT</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef6f778294e73998</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>Senior Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Bain &amp; Company</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2661,12 +2661,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,77 +2796,77 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Sr. Associate, Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Community Federal Savings Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Data Solution Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>RA Capital Management</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,19 +2911,19 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2932,11 +2932,11 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>SRE / DevOps Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>Full-Stack Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>RA Capital Management</t>
+          <t>Social Impact</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior AI &amp; Data Engineer</t>
+          <t>Aerospace Software DevOps Engineer II</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Alamar Biosciences</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Fremont, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>ECS, RDS, Databricks, Unity Catalog, BigQuery, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1884155644ac6742</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,190 +3146,15 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>SRE / DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Full-Stack Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Social Impact</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Aerospace Software DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>

--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Senior Data Engineer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>L.E.K. Consulting</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddcbcd3fcf90b62</t>
+          <t>https://www.indeed.com/viewjob?jk=94da66580e29e534</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data &amp; Analytics Senior Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>L.E.K. Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Unity Catalog, GCP, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c24ee3772fb2025</t>
+          <t>https://www.indeed.com/viewjob?jk=9ddcbcd3fcf90b62</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Quality</t>
+          <t>Senior Associate - AI Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Sidley Austin</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,17 +556,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, S3, IAM, Databricks, Hadoop, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6913762be867dbf6</t>
+          <t>https://www.indeed.com/viewjob?jk=9cc5523e609d6490</t>
         </is>
       </c>
     </row>
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AWS, python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,77 +626,77 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,77 +706,77 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Sr Forward Deployed Engineer (Foundry)</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trinity Industries</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e98784d3b069887</t>
+          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -806,37 +806,37 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=154aec3c659c637e</t>
+          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b763ccac8082bb3</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
@@ -923,17 +923,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer, Marketing Data Operations</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,102 +986,102 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Centric Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, RDS, Scala, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46cdeb4b1af72885</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Scala, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=688d23a37649aa4e</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>Senior Azure Data Engineer (W2 only)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Highbrow Technology Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer (W2 only)</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Highbrow Technology Inc</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
+          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>System Engineer-Platform/Kafka/Messaging</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>IAM, RDS, GCP, Dataflow, Spark, Scala, Kafka, Kafka Connect, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=7af3032d6f77f72a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Freddie Mac</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, IAM, RDS, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b2c6986e7938de04</t>
+          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Intregration Engineer</t>
+          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IntegraTouch</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Cloud Storage, Scala, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,19 +1371,19 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=189b52949d35286b</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1392,11 +1392,11 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>System Engineer-Platform/Kafka/Messaging</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Spark, Scala, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af3032d6f77f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
+          <t>AI Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Success Academy Charter Schools</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
+          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Engineer, Energy</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brookshire, TX, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,42 +1571,42 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Ideal Business Advisors</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
+          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Energy</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Dearborn, MI, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Spark, Scala, MLOps</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6725bf29a07dcb85</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
+          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
+          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
+          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Software Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
+          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Oracle Unity/Fusion Customer Data Platform (CDP) Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Hashout Technologies, Inc.</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05820054e138dd33</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer / Database Administrator</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
+          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Goodwill Industries of Ky., Inc.</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4de6845b355390df</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>Salesforce Enterprise Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Purple Austyn Technologies</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,207 +2526,207 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1f1526a2cc9c583</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66f736568439fa09</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Sr. Associate, Cloud Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Community Federal Savings Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d38e83f9c27ee7f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1b55ac084d2b38e</t>
+          <t>https://www.indeed.com/viewjob?jk=f980bce192a46430</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Quality Assurance Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bedeff840282078</t>
+          <t>https://www.indeed.com/viewjob?jk=5f42a2e47343013f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer</t>
+          <t>Advanced AI Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Bain &amp; Company</t>
+          <t>Honeywell</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, PostgreSQL, ETL, Docker, Kubernetes, AKS, pytest</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4d440465d091eb4</t>
+          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>SRE / DevOps Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Full-Stack Platform Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>Social Impact</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>Digital iTechnology</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2792,38 +2792,38 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>Aerospace Software DevOps Engineer II</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Blue Origin</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,19 +2841,19 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Solution Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>RA Capital Management</t>
+          <t>Nexstar Media Group, Inc.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2910,251 +2910,6 @@
         </is>
       </c>
       <c r="G71" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=dbb511c116964595</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Senior Data Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Core BTS</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D72" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Advanced AI Engineer</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Honeywell</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D73" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>SRE / DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Full-Stack Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Social Impact</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Aerospace Software DevOps Engineer II</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Blue Origin</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>

--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Data Architect</t>
+          <t>Asset &amp; Wealth Management, Business Analytics, Associate - New York</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WinWire</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alameda, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.1</v>
+        <v>22.2</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, GCP, BigQuery</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,42 +496,42 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=94da66580e29e534</t>
+          <t>https://www.indeed.com/viewjob?jk=d4ad76c8612e4a09</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data &amp; Analytics Senior Data Engineer</t>
+          <t>AWS Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>L.E.K. Consulting</t>
+          <t>WinWire</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Alameda, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, GCP, BigQuery, Vertex AI, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, IAM, RDS</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ddcbcd3fcf90b62</t>
+          <t>https://www.indeed.com/viewjob?jk=94da66580e29e534</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, python</t>
+          <t>AI/ML Intern</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>Xpedient Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1d8e827779774e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - AWS, python</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
         </is>
       </c>
     </row>
@@ -701,37 +701,37 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -776,102 +776,102 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
+          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Analyst / Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Diné Development Corporation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer, Marketing Data Operations</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
+          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>System Engineer- Platform/API Gateway</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
+          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,42 +976,42 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>System Engineer- Platform/API Gateway</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,42 +1021,42 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
@@ -1068,20 +1068,20 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer (W2 only)</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Highbrow Technology Inc</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,29 +1186,29 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>System Engineer-Platform/Kafka/Messaging</t>
+          <t>Senior Azure Data Engineer (W2 only)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>Highbrow Technology Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, Dataflow, Spark, Scala, Kafka, Kafka Connect, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7af3032d6f77f72a</t>
+          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Client Resources, Inc.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Omaha, NE, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
+          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
+          <t>Senior AWS Solution Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Random Bit</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,42 +1361,42 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Landmark</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
+          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>AI Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Success Academy Charter Schools</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, Azure, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f69cae0b073ffd83</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forward Deployed Engineer, Energy</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tesla</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brookshire, TX, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,77 +1571,77 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Power BI, Tableau, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed396163c7720de0</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Zayo Group</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
+          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>Bedrock Data</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
+          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Ideal Business Advisors</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,34 +1746,34 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Software Engineer - Early Career - Landmark</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Halliburton</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Glendale, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
+          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Anaheim, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
+          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Database Engineer / Database Administrator</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Santa Clarita, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
+          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>BI Developer Services – Level III - 26-05818</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NavitasPartners</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Software Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Senior Business Systems &amp; Integrations Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,34 +2341,34 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Salesforce Enterprise Architect</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Purple Austyn Technologies</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,42 +2481,42 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, ETL, ELT, CI/CD</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ef8a774183b65cc</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Travelers</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,59 +2596,59 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Analytics Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Interworks</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
+          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f980bce192a46430</t>
+          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Data Engineer II - Analytics</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f42a2e47343013f</t>
+          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SRE / DevOps Engineer</t>
+          <t>Sr. Associate, Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Community Federal Savings Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Engineer</t>
+          <t>Senior Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Social Impact</t>
+          <t>Core BTS</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
+          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Digital iTechnology</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+          <t>https://www.indeed.com/viewjob?jk=da9c3829227dd781</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Aerospace Software DevOps Engineer II</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Blue Origin</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2b1191705b29853</t>
+          <t>https://www.indeed.com/viewjob?jk=65b067d12eb88dd1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ad78f557a45964</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Nexstar Media Group, Inc.</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,15 +2901,295 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=acdf9d3eb5360a9e</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f980bce192a46430</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Quality Assurance Engineer</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5f42a2e47343013f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Digital iTechnology</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>SRE / DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Full-Stack Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Social Impact</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Advanced AI Engineer</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>AI/ML Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Nexstar Media Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>

--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,17 +748,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Data/AI Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,69 +766,69 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, PySpark, Snowflake</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac01b3454ac02ccf</t>
+          <t>https://www.indeed.com/viewjob?jk=6b7b2e289fa4a81b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Analyst / Data Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Diné Development Corporation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Scala, Oracle, SQL Server</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d92003d1693fcf89</t>
+          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AI-Native Builder</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Newpage Digital Healthcare solutions</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, Cassandra, CI/CD, Jenkins</t>
+          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,7 +846,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01411b771339e7f8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
         </is>
       </c>
     </row>
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa0b54505ba83c83</t>
+          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
         </is>
       </c>
     </row>
@@ -916,59 +916,59 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788be6fbb8bd5c28</t>
+          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI-Native Builder</t>
+          <t>Data Engineer, Marketing Data Operations</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Newpage Digital Healthcare solutions</t>
+          <t>Universal Orlando Resort</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Vertex AI, Spark, Scala, MLOps, MLflow, CI/CD</t>
+          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01d2969a0188cb3d</t>
+          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer/Sr. Data Engineer -ITDDP (Contractual)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Georgia-Pacific</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Star Schema, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7979c28cb86f5690</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>System Engineer- Platform/API Gateway</t>
+          <t>Senior Software Engineer – Data Engineering (GCP &amp; AI) (contract)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>O'Reilly Auto Parts</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Springfield, MO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, Snowflake, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
+          <t>https://www.indeed.com/viewjob?jk=864bf732311fb751</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer, Marketing Data Operations</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Universal Orlando Resort</t>
+          <t>Georgia-Pacific</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, BigQuery, Hadoop, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, Athena, S3, ECS, RDS, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50262f2646c95e45</t>
+          <t>https://www.indeed.com/viewjob?jk=cc070bfe12f04a4e</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>System Engineer- Platform/API Gateway</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>O'Reilly Auto Parts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Springfield, MO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>API Gateway, IAM, RDS, Azure, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9f3ba65fc8111094</t>
         </is>
       </c>
     </row>
@@ -1103,12 +1103,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Recutify Inc.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,59 +1126,59 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Encino, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>GCP Data Eng</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,34 +1256,34 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Azure Data Engineer (W2 only)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Highbrow Technology Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Medallion Architecture, Spark, PySpark, Scala, Data Modeling, ELT</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3be2ecbf806de066</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Client Resources, Inc.</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Omaha, NE, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Scala, Snowflake, Oracle, SQL Server, MongoDB, Data Modeling, Dimensional Modeling</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cef42acc1d37c051</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior AWS Solution Architect</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Random Bit</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Landmark</t>
+          <t>Senior AWS Solution Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>Random Bit</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=198b17d882618b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
         </is>
       </c>
     </row>
@@ -1483,25 +1483,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Database Engineer (AWS/Snowflake/Postgres)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ea429cd1057282d</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analytics Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Zayo Group</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,69 +1676,69 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa5c60daa2eb488c</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Deployment Engineer (Infrastructure &amp; DevOps)</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Bedrock Data</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73d8155dedb8c388</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Software Engineer, Build and Release Management</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
+          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Total Wine &amp; More</t>
+          <t>Ideal Business Advisors</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
+          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
+          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Software Engineer - Early Career - Landmark</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Halliburton</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MongoDB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c2850e7510faaa4</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Cloud Aviation</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>El Monte, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
         </is>
       </c>
     </row>
@@ -2078,17 +2078,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Database Engineer / Database Administrator</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>FinQuery</t>
+          <t>Total Wine &amp; More</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,29 +2096,29 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
+          <t>RDS, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, ETL, ELT, dbt, Power BI</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
+          <t>https://www.indeed.com/viewjob?jk=2d61f658ab71dc3d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Database Engineer / Database Administrator</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>FinQuery</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2127,38 +2127,38 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Snowflake, SQL Server, PostgreSQL, ELT, Tableau, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=308cbdae7b1e0202</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>Software Engineer (Generative AI)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Business Systems &amp; Integrations Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>IAM, RDS, Azure, Scala, PostgreSQL, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc5ce5e437bc35</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Business Systems &amp; Integrations Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer II -- Enterprise AI Products Value Stream</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Travelers</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, MongoDB, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=72ccfb0ea0091329</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d13d49983362928</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Architect</t>
+          <t>Senior Full-Stack Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Interworks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Glue, RDS, Databricks, BigQuery, Snowflake, Databricks Lakehouse, Data Modeling, ELT, dbt, Tableau</t>
+          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f63a609ce9a0e0e</t>
+          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer II - Analytics</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,59 +2666,59 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Analytics Engineer</t>
+          <t>Data Engineer II - Analytics</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Core BTS</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Medallion Architecture, Scala, Data Modeling, Kimball, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2c2350b85e1faca</t>
+          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9c3829227dd781</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>Sr. Associate, Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>Community Federal Savings Bank</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,17 +2831,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b067d12eb88dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ad78f557a45964</t>
+          <t>https://www.indeed.com/viewjob?jk=da9c3829227dd781</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdf9d3eb5360a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=65b067d12eb88dd1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f980bce192a46430</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ad78f557a45964</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Quality Assurance Engineer</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, SQS, API Gateway, ECS, PostgreSQL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f42a2e47343013f</t>
+          <t>https://www.indeed.com/viewjob?jk=acdf9d3eb5360a9e</t>
         </is>
       </c>
     </row>
@@ -3122,76 +3122,6 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9158d7ecaabe631d</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>AI/ML Engineer</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Nexstar Media Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Vertex AI, Spark, MLOps, MLflow, CI/CD</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=746360ee3987922f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-05-20.xlsx
+++ b/results/job_matches_2026-05-20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI/ML Intern</t>
+          <t>Data Engineer - AWS, python</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Xpedient Technologies</t>
+          <t>JSR Tech Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Newark, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Vertex AI, Scala, PostgreSQL, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1d8e827779774e</t>
+          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer - AWS, python</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>JSR Tech Consulting</t>
+          <t>The Walt Disney Company</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Newark, NJ, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, Step Functions, S3, SQS</t>
+          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fc48402a0ee4138</t>
+          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
         </is>
       </c>
     </row>
@@ -701,47 +701,47 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ef768a7022d9b02</t>
+          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr AI/ML Engineer - Remote Nationwide or Hybrid in MN/DC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The Walt Disney Company</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SQS, ECS, IAM, RDS, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4d2f3a6f6a24726d</t>
+          <t>https://www.indeed.com/viewjob?jk=a5428c5fe3301bb2</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Recutify Inc.</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, GCP, Hadoop, HDFS, Hive, YARN, Spark, PySpark, Scala, Oracle</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28e1c461015035ce</t>
+          <t>https://www.indeed.com/viewjob?jk=32851dd10ee0e5da</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Encino, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,104 +1151,104 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Spark, PySpark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5196076aab88a07</t>
+          <t>https://www.indeed.com/viewjob?jk=708d5186ef13d22a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>GCP Data Eng</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
+          <t>https://www.indeed.com/viewjob?jk=8ab11bf9d3a0cb66</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ETL Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Triwave Solutions Inc</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, IAM, RDS, Scala, Kafka, Snowflake, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4179f9ef43c111</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
+          <t>GCP Data Eng</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
+          <t>GCP, Hadoop, Hive, Spark, PySpark, Scala, Kafka, ETL, Jenkins, Jenkins</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
+          <t>https://www.indeed.com/viewjob?jk=4aa07fecdad59559</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>ETL Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Triwave Solutions Inc</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, Athena, Step Functions, S3, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
+          <t>https://www.indeed.com/viewjob?jk=67cc5c5d1b62b505</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
+          <t>Cloud Database Administrator (DBA)/ETL Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Barrett-Jackson Auction Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
+          <t>AWS, S3, RDS, Scala, Kafka, Snowflake, Time Travel, Oracle, SQL Server, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
+          <t>https://www.indeed.com/viewjob?jk=98b32025713e041a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Engineer (Backend) - MTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Scala, NoSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
+          <t>https://www.indeed.com/viewjob?jk=913ce0d28b943134</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior AWS Solution Architect</t>
+          <t>Data Engineer (Warehouse, BI &amp; SQL DBA)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Random Bit</t>
+          <t>Barrett-Jackson Auction Company</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
+          <t>Azure, Data Factory, Spark, Scala, Snowflake, SQL Server, Data Modeling, Dimensional Modeling, Kimball, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
+          <t>https://www.indeed.com/viewjob?jk=a2a5363a406f3ade</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior DB engineer</t>
+          <t>Senior AWS Solution Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Random Bit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, S3, SQS, SNS, IAM, RDS, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
+          <t>https://www.indeed.com/viewjob?jk=a5f8e7a290e072e8</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Ops Engineer</t>
+          <t>Software Engineer (Backend) - MTS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>National Debt Relief</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,42 +1466,42 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
+          <t>https://www.indeed.com/viewjob?jk=aa29de43e62d8b14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DB engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Newity LLC</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Cassandra, NoSQL, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
+          <t>https://www.indeed.com/viewjob?jk=560a0ac785ae0307</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
+          <t>Senior Machine Learning Ops Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Infinitive Inc</t>
+          <t>National Debt Relief</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
+          <t>AWS, ECS, RDS, Scala, Snowflake, dbt, MLflow, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
+          <t>https://www.indeed.com/viewjob?jk=d62f3b2380e0b366</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer (Temporary)</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Brooks Running</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
+          <t>https://www.indeed.com/viewjob?jk=2139ccd23148ef97</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Microsoft Analytics Data Engineer Senior Consultant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Air Today USA</t>
+          <t>Protiviti</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Data Modeling, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
+          <t>https://www.indeed.com/viewjob?jk=979fd479106b8582</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Mid-level DevOps Engineer</t>
+          <t>Cloud AWS Support Reliability Engineer (SRE)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ella Wholesales Coffee</t>
+          <t>Federal Reserve Bank of New York</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, SNS, ECS, IAM, RDS, Scala, Oracle</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
+          <t>https://www.indeed.com/viewjob?jk=397e7786631910d4</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Newity LLC</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, ECS, IAM, RDS, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f118becd7bebc8f7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II (US)</t>
+          <t>Data Engineer (Python/PySpark/Apache Spark)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TD</t>
+          <t>Infinitive Inc</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mount Laurel, NJ, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,42 +1711,42 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
+          <t>AWS, Azure, Spark, PySpark, Scala, Spark Streaming, Data Modeling, ETL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=2b4cfb81cc411bf7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr Software Engineer, Build and Release Management</t>
+          <t>Senior Machine Learning Engineer (Temporary)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cboe Global Markets</t>
+          <t>Brooks Running</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
+          <t>https://www.indeed.com/viewjob?jk=31e77238a1b70a49</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ideal Business Advisors</t>
+          <t>Air Today USA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,42 +1791,42 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
+          <t>https://www.indeed.com/viewjob?jk=c73ef9f43ca54c71</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>AI Commercial &amp; ML Ops Engineer</t>
+          <t>Mid-level DevOps Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>MGM Resorts International</t>
+          <t>Ella Wholesales Coffee</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, MySQL, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
+          <t>https://www.indeed.com/viewjob?jk=02374e2f05fa51aa</t>
         </is>
       </c>
     </row>
@@ -1838,55 +1838,55 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cloud Aviation</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>El Monte, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecef5b286b3de60</t>
+          <t>https://www.indeed.com/viewjob?jk=b8bd188504a235ef</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Intelligence Developer</t>
+          <t>Data Engineer II (US)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>TD</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Mount Laurel, NJ, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
+          <t>RDS, Databricks, Spark, Scala, Data Modeling, Dimensional Modeling, ETL, ELT, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
+          <t>https://www.indeed.com/viewjob?jk=acd3a2400ded0ef7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Platform Architect - AI</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Flex</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Glendale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d10eba39e5e728f7</t>
+          <t>https://www.indeed.com/viewjob?jk=e294cc6d33384a45</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Sr Software Engineer, Build and Release Management</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Cboe Global Markets</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Anaheim, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,34 +1956,34 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=553af7a9ea2c94ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fe77948a6745c2be</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>Ideal Business Advisors</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Santa Clarita, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Spark, Spark Streaming, Kafka, Snowflake, ETL, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9008cdf9aec7fb4b</t>
+          <t>https://www.indeed.com/viewjob?jk=5e07e4d5100d0a09</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>AI Commercial &amp; ML Ops Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>MGM Resorts International</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala, MLflow, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b372a3e7801d9f67</t>
+          <t>https://www.indeed.com/viewjob?jk=b3de78a500e2bdfb</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BI Developer Services – Level III - 26-05818</t>
+          <t>Business Intelligence Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NavitasPartners</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, SQL Server, Data Modeling, Dimensional Modeling, Star Schema, ETL</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45b94dc1f208983</t>
+          <t>https://www.indeed.com/viewjob?jk=225bdb7f78f14470</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Periscope</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>McKinsey &amp; Company</t>
+          <t>CG Infinity</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
+          <t>AWS, Redshift, Azure, GCP, Spark, Scala, Snowflake, Star Schema, Tableau, Git</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=0a20b18aa66e51d2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Humbly Confident Senior Laravel Engineer</t>
+          <t>Senior Data Engineer - Periscope</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Chiro Cat</t>
+          <t>McKinsey &amp; Company</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
+          <t>Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, Spark, Scala, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
+          <t>https://www.indeed.com/viewjob?jk=8cd4f1b922a309e4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer (Generative AI)</t>
+          <t>Humbly Confident Senior Laravel Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Chiro Cat</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Google Cloud Platform, GCP, BigQuery, Vertex AI, Hadoop, Snowflake, MLOps, CI/CD, Git</t>
+          <t>AWS, S3, ECS, RDS, Scala, PostgreSQL, MySQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-28</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da1e181dd87c6910</t>
+          <t>https://www.indeed.com/viewjob?jk=3d426212b47f2cb5</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Intone Networks</t>
+          <t>Clayco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6fb9d94196cc44d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTIMindtree</t>
+          <t>Intone Networks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>IAM, RDS, Azure, Scala, PostgreSQL, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>RDS, Azure, Synapse Analytics, Databricks, Cloud Storage, Spark, PySpark, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7dcc5ce5e437bc35</t>
+          <t>https://www.indeed.com/viewjob?jk=f9d0b722ecec30e9</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Business Systems &amp; Integrations Architect</t>
+          <t>Sr. Distributed Systems Engineer, Energy Service Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Tesla</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Spark, PySpark, Scala, Spark Streaming, Kafka, ELT, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b311adc4e009a8c4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Weyerhaeuser</t>
+          <t>LTIMindtree</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
+          <t>IAM, RDS, Azure, Scala, PostgreSQL, MySQL, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
+          <t>https://www.indeed.com/viewjob?jk=7dcc5ce5e437bc35</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Database Engineer</t>
+          <t>Senior Business Systems &amp; Integrations Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Chess.com</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
+          <t>https://www.indeed.com/viewjob?jk=6abc49ee6c2f3b4f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Portfolio BI</t>
+          <t>Weyerhaeuser</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MLOps, MLflow, Airflow, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
+          <t>https://www.indeed.com/viewjob?jk=d9012b2ffe5f7c5e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Python Full Stack Developer</t>
+          <t>Database Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>Chess.com</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Scala, MySQL, Cassandra, Data Modeling, ETL, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
+          <t>https://www.indeed.com/viewjob?jk=89d4f32f720c7b3e</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Full Stack Quantitative Developer - NYC / Dallas / Los Angeles</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Portfolio BI</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, ECS, RDS, Azure, Scala, NoSQL, Tableau, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
+          <t>https://www.indeed.com/viewjob?jk=b6e72e9173a4b1e5</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
+          <t>Python Full Stack Developer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>California State Personnel Board</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
+          <t>https://www.indeed.com/viewjob?jk=71f910656c4ac5af</t>
         </is>
       </c>
     </row>
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
+          <t>https://www.indeed.com/viewjob?jk=7b1897a63fde0954</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Full-Stack Software Engineer</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, Azure, GCP, Cloud Storage, MongoDB, NoSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07961822c801c505</t>
+          <t>https://www.indeed.com/viewjob?jk=17aeeb541c761336</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Intelligence Analyst - Harrisburg, PA</t>
+          <t>INFORMATION TECHNOLOGY SPECIALIST II</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>AAA Central Penn</t>
+          <t>California State Personnel Board</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
+          <t>AWS, S3, API Gateway, IAM, RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
+          <t>https://www.indeed.com/viewjob?jk=637b19c57d2d2f1f</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Field Engineer</t>
+          <t>Business Intelligence Analyst - Harrisburg, PA</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Florence HC</t>
+          <t>AAA Central Penn</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Harrisburg, PA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, Data Modeling, Dimensional Modeling, Kimball, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
+          <t>https://www.indeed.com/viewjob?jk=a7c5dcb3f5dd6592</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Field Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Clearwater Analytics (CWAN)</t>
+          <t>Florence HC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
+          <t>https://www.indeed.com/viewjob?jk=a0f35f177eb851ec</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer II - Analytics</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RevSpring, Inc</t>
+          <t>Clearwater Analytics (CWAN)</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
+          <t>SQS, SNS, Hadoop, Hive, HBase, Spark, Scala, Kafka, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
+          <t>https://www.indeed.com/viewjob?jk=4594ef27276bcddb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Consultant</t>
+          <t>Data Engineer II - Analytics</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Releady</t>
+          <t>RevSpring, Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Data Modeling, ETL, Tableau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
+          <t>https://www.indeed.com/viewjob?jk=15bd37695704d0b2</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Associate, Cloud Engineer</t>
+          <t>Data Engineer - Consultant</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Community Federal Savings Bank</t>
+          <t>Releady</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Sacramento, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
+          <t>Azure, Scala, Snowflake, Oracle, SQL Server, dbt, Tableau, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
+          <t>https://www.indeed.com/viewjob?jk=26c8d9977ea88967</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Informatics Architect</t>
+          <t>Sr. Associate, Cloud Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Gritter Francona, Inc</t>
+          <t>Community Federal Savings Bank</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,17 +2866,17 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Azure, Scala, Terraform, Docker</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da9c3829227dd781</t>
+          <t>https://www.indeed.com/viewjob?jk=6632526b69079b6f</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65b067d12eb88dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=da9c3829227dd781</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7ad78f557a45964</t>
+          <t>https://www.indeed.com/viewjob?jk=65b067d12eb88dd1</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acdf9d3eb5360a9e</t>
+          <t>https://www.indeed.com/viewjob?jk=d7ad78f557a45964</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Full Stack Engineer - Remote -W2 Only</t>
+          <t>Informatics Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Digital iTechnology</t>
+          <t>Gritter Francona, Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, SQL Server, Fact Tables, Dimension Tables, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
+          <t>https://www.indeed.com/viewjob?jk=acdf9d3eb5360a9e</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SRE / DevOps Engineer</t>
+          <t>Full Stack Engineer - Remote -W2 Only</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Digital iTechnology</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, GitHub Actions, Docker, Git, Bitbucket, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
+          <t>https://www.indeed.com/viewjob?jk=ef52a4058b83ad57</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Full-Stack Platform Engineer</t>
+          <t>SRE / DevOps Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Social Impact</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
+          <t>https://www.indeed.com/viewjob?jk=6b064c172d457476</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Advanced AI Engineer</t>
+          <t>Full-Stack Platform Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Honeywell</t>
+          <t>Social Impact</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,15 +3111,50 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, Power BI, Tableau, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ecea58c06ba3a52</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Advanced AI Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Honeywell</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Charlotte, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
           <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, MLOps, MLflow, CI/CD</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-05-20</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6cfea9e97e390496</t>
         </is>
